--- a/storage/imports/templates/services.xlsx
+++ b/storage/imports/templates/services.xlsx
@@ -329,7 +329,7 @@
     <t>SRV-PHYSIO-01</t>
   </si>
   <si>
-    <t>Expert physiotherapy in Bangalore (Arekere belt).</t>
+    <t>Expert physiotherapy in Bangalore (Karnataka belt).</t>
   </si>
   <si>
     <t>parent_service_code</t>
